--- a/samples/O_存货明细表.xlsx
+++ b/samples/O_存货明细表.xlsx
@@ -66,12 +66,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,143 +438,485 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>存货类别</t>
+          <t>物料编码</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>期初余额</t>
+          <t>物料名称</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>本期入库</t>
+          <t>规格型号</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>本期出库</t>
+          <t>期初数量</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>期末余额</t>
+          <t>期初金额</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>库龄&lt;1年</t>
+          <t>本期入库数量</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>库龄1-2年</t>
+          <t>本期入库金额</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>库龄&gt;2年</t>
+          <t>本期出库数量</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>本期出库金额</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>期末数量</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>期末金额</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>存放仓库</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>原材料</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>3200000</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>8500000</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>7900000</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>3800000</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>3200000</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>500000</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>100000</v>
-      </c>
+          <t>CL-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>冷轧钢板</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Q235B 2.0mm</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>285000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>420</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>798000</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>380</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>722000</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>361000</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>A1仓库</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>库存商品-A</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>2800000</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>16000000</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>15800000</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="G3" s="2" t="n">
+          <t>CL-002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>不锈钢板</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>304 1.5mm</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>320000</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>800000</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>720000</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K3" s="3" t="n">
         <v>400000</v>
       </c>
-      <c r="H3" s="2" t="n">
-        <v>100000</v>
-      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>A2仓库</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>库存商品-B</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>2300000</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>11700000</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>2600000</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>500000</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>100000</v>
+          <t>CL-003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>铝合金型材</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>6063-T5</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>240000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>700000</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>330</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>660000</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>280000</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>A1仓库</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CP-001</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>智能控制器</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>ZK-2024A</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>580000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>480</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>1392000</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>1305000</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>667000</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>B1仓库</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>库存商品</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>CP-002</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>传感器模块</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>CG-2024B</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>360000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>840000</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>320</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>768000</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>432000</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>B1仓库</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>库存商品</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>CP-003</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>工业机器人臂</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>RB-6A</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>B2仓库</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>库存商品，关注可变现净值</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>CP-004</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>伺服电机</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>SV-750W</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>280000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>700000</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>672000</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>308000</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>B2仓库</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>库存商品</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>WT-001</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>外协加工件</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>定制</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>360000</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>330000</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>180000</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>C1仓库</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>委托加工物资</t>
+        </is>
       </c>
     </row>
   </sheetData>
